--- a/Sample_run/1/student/duongnthe186310/TC4/GradeDetail.xlsx
+++ b/Sample_run/1/student/duongnthe186310/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1289,7 +1289,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1345,7 +1345,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1398,7 +1398,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>40664</x:v>
+        <x:v>51698</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
